--- a/college-posters/data/字段表_211第六批.xlsx
+++ b/college-posters/data/字段表_211第六批.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -505,68 +505,68 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>林业与生态环保、木材与家居制造、党政机关与事业单位</t>
+          <t>主校区：哈尔滨和兴路校区；实验林场：校内城市林业示范基地；冰雪校园：冬季冰雪景观</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>东北林业大学</t>
+          <t>东北农业大学</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>主校区：哈尔滨和兴路校区；实验林场：校内城市林业示范基地；冰雪校园：冬季冰雪景观</t>
+          <t>农学、动物科学、动物医学、食品科学与工程、农业机械化及其自动化、园艺</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>东北林业大学</t>
+          <t>东北农业大学</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>主校区：哈尔滨香坊区；试验田：黑土地实践基地；冰雪校园：冬季冰雪景观</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>东北农业大学</t>
+          <t>辽宁大学</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>农学、动物科学、动物医学、食品科学与工程、农业机械化及其自动化、园艺</t>
+          <t>经济学、金融学、国际经济与贸易、法学、汉语言文学、历史学</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -588,73 +588,73 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>东北农业大学</t>
+          <t>辽宁大学</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>农业与畜牧企业、食品与乳业、党政机关与事业单位</t>
+          <t>崇山校区：沈阳老校区；蒲河校区：沈北主校区；武圣校区：辽阳校区</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>东北农业大学</t>
+          <t>新疆大学</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>主校区：哈尔滨香坊区；试验田：黑土地实践基地；冰雪校园：冬季冰雪景观</t>
+          <t>化学、计算机科学与技术、电气工程及其自动化、汉语言文学、法学、旅游管理</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>东北农业大学</t>
+          <t>新疆大学</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>博达校区：乌鲁木齐新校区；友好校区：老校区；北校区：工科校区</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>辽宁大学</t>
+          <t>四川农业大学</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>经济学、金融学、国际经济与贸易、法学、汉语言文学、历史学</t>
+          <t>农学、动物科学、动物医学、园艺、林学、食品科学与工程</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -676,73 +676,73 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>辽宁大学</t>
+          <t>四川农业大学</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>金融与经济、党政机关与事业单位、东北本地企业</t>
+          <t>雅安校区：青衣江畔的老校区；成都校区：温江校区；都江堰校区：林学与旅游校区</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>辽宁大学</t>
+          <t>石河子大学</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>崇山校区：沈阳老校区；蒲河校区：沈北主校区；武圣校区：辽阳校区</t>
+          <t>化学工程与工艺、临床医学、农学、动物医学、水利水电工程、师范类专业</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>辽宁大学</t>
+          <t>石河子大学</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>北区：主校区；中区：医学院所在地；军垦博物馆：石河子市内的兵团历史馆</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>新疆大学</t>
+          <t>宁夏大学</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>化学、计算机科学与技术、电气工程及其自动化、汉语言文学、法学、旅游管理</t>
+          <t>化学工程与工艺、葡萄与葡萄酒工程、生态学、农学、法学、汉语言文学</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -764,73 +764,73 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>新疆大学</t>
+          <t>宁夏大学</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>党政机关与事业单位、能源与化工、新疆本地企业</t>
+          <t>贺兰山校区：银川主校区；文萃校区：老校区；怀远校区：银川校区</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>新疆大学</t>
+          <t>延边大学</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>博达校区：乌鲁木齐新校区；友好校区：老校区；北校区：工科校区</t>
+          <t>朝鲜语、日语、临床医学、药学、汉语言文学、旅游管理</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>新疆大学</t>
+          <t>延边大学</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>主校区：延吉市区；布尔哈通河：流经延吉的河流；图书馆：校园标志建筑</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>四川农业大学</t>
+          <t>西藏大学</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>农学、动物科学、动物医学、园艺、林学、食品科学与工程</t>
+          <t>生态学、藏语言文学、旅游管理、计算机科学与技术、临床医学、艺术类专业</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -852,572 +852,66 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>四川农业大学</t>
+          <t>西藏大学</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>就业方向</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>农业与种业、畜牧与食品、党政机关与事业单位</t>
+          <t>布达拉宫为拉萨城市地标，非校内景观，已在说明中注明</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>待核就业质量报告</t>
+          <t>待核官网介绍</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>四川农业大学</t>
+          <t>青海大学</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>校园风物</t>
+          <t>王牌专业</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>雅安校区：青衣江畔的老校区；成都校区：温江校区；都江堰校区：林学与旅游校区</t>
+          <t>生态学、草业科学、动物医学、临床医学、水利水电工程、土木工程</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>待核官网介绍</t>
+          <t>待核当年招生专业目录</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>四川农业大学</t>
+          <t>青海大学</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>选科要求</t>
+          <t>校园风物</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
+          <t>主校区：西宁城北区；医学部：医学院校区；湟水河：流经西宁的河流</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>石河子大学</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>化学工程与工艺、临床医学、农学、动物医学、水利水电工程、师范类专业</t>
-        </is>
-      </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>石河子大学</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>兵团与新疆企事业、医疗卫生、农业与化工</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>石河子大学</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>北区：主校区；中区：医学院所在地；军垦博物馆：石河子市内的兵团历史馆</t>
-        </is>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
           <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>石河子大学</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>宁夏大学</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>校训</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>宁夏大学校训原文未核到，海报竖排改放运营寄语“塞上明珠”，印章写“寄语”</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>宁夏大学</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>化学工程与工艺、葡萄与葡萄酒工程、生态学、农学、法学、汉语言文学</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>宁夏大学</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>能源化工、葡萄酒与农业、党政机关与事业单位</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>宁夏大学</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>贺兰山校区：银川主校区；文萃校区：老校区；怀远校区：银川校区</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>宁夏大学</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>延边大学</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>朝鲜语、日语、临床医学、药学、汉语言文学、旅游管理</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>延边大学</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>外贸与翻译、医疗卫生、党政机关与事业单位</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>延边大学</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>主校区：延吉市区；布尔哈通河：流经延吉的河流；图书馆：校园标志建筑</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>延边大学</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>西藏大学</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>校训</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>西藏大学校训原文未核到，海报竖排改放运营寄语“雪域学府”，印章写“寄语”</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>西藏大学</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>生态学、藏语言文学、旅游管理、计算机科学与技术、临床医学、艺术类专业</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>西藏大学</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>党政机关与事业单位、教育与文化、高原生态与环保</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>西藏大学</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>布达拉宫为拉萨城市地标，非校内景观，已在说明中注明</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>西藏大学</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>青海大学</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>校训</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>青海大学校训原文未核到，海报竖排改放运营寄语“高原学府”，印章写“寄语”</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>青海大学</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>王牌专业</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>生态学、草业科学、动物医学、临床医学、水利水电工程、土木工程</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t>待核当年招生专业目录</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>青海大学</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>就业方向</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>党政机关与事业单位、医疗卫生、高原农牧与生态</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>青海大学</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>校园风物</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>主校区：西宁城北区；医学部：医学院校区；湟水河：流经西宁的河流</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>待核官网介绍</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>青海大学</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>选科要求</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>理工类专业：物理 + 化学；人文社科类：要求较宽，以当年招生章程为准</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
         </is>
       </c>
     </row>
@@ -1584,22 +1078,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>西藏大学校训原文未核到，海报竖排改放运营寄语“雪域学府”，印章写“寄语”</t>
+          <t>团结 勤奋 求实 创新；已替换原运营寄语</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>雪域 学府</t>
+          <t>团结勤奋 求实创新</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
+          <t>维基镜像、买购网（两源一致）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>较可靠，待核官网</t>
         </is>
       </c>
     </row>
@@ -1981,9 +1475,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2106,12 +1600,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -2342,22 +1836,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>青海大学校训原文未核到，海报竖排改放运营寄语“高原学府”，印章写“寄语”</t>
+          <t>志比昆仑 学竞江河；已替换原运营寄语</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>高原 学府</t>
+          <t>志比昆仑 学竞江河</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
+          <t>中华网、学校介绍页（两源一致）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>较可靠，待核官网</t>
         </is>
       </c>
     </row>
@@ -2739,9 +2233,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -2864,12 +2358,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -3497,9 +2991,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -3622,12 +3116,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -4255,9 +3749,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -4380,12 +3874,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5013,9 +4507,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5138,12 +4632,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -5771,9 +5265,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -5896,12 +5390,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -6529,9 +6023,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -6654,12 +6148,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7287,9 +6781,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -7412,12 +6906,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -7648,22 +7142,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>宁夏大学校训原文未核到，海报竖排改放运营寄语“塞上明珠”，印章写“寄语”</t>
+          <t>尚德勤学 求是创新；已替换原运营寄语</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>塞上 明珠</t>
+          <t>尚德勤学 求是创新</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>待核（校训原文）</t>
+          <t>维基百科等（两源一致）</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>较可靠，待核官网</t>
         </is>
       </c>
     </row>
@@ -8045,9 +7539,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8170,12 +7664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
@@ -8803,9 +8297,9 @@
           <t>就业质量报告、公开报道，概括整理</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>待核就业质量报告</t>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>运营概括（行业方向，非统计数据）</t>
         </is>
       </c>
     </row>
@@ -8928,12 +8422,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>分省招生计划、招生章程</t>
-        </is>
-      </c>
-      <c r="F21" s="3" t="inlineStr">
-        <is>
-          <t>待核2027年招生章程</t>
+          <t>教育部《普通高校本科招生专业选考科目要求指引（通用版）》、招生章程</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>较可靠（符合教育部选科指引：理工医农类原则上物理+化学）；具体专业以2027年招生章程为准</t>
         </is>
       </c>
     </row>
